--- a/data/trans_bre/LAWTONB_2R2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/LAWTONB_2R2-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,06; 12,68</t>
+          <t>1,14; 12,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,68; 15,8</t>
+          <t>3,45; 16,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,82; 17,66</t>
+          <t>5,58; 18,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,6; 20,76</t>
+          <t>9,54; 20,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,72; 50,43</t>
+          <t>3,37; 46,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,61; 58,08</t>
+          <t>9,82; 60,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,28; 75,7</t>
+          <t>17,95; 75,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22,85; 61,91</t>
+          <t>21,83; 58,14</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 20,6</t>
+          <t>-6,92; 20,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 20,14</t>
+          <t>-4,13; 20,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,06; 26,81</t>
+          <t>8,79; 26,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,51; 8,93</t>
+          <t>-13,63; 9,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-43,32; 170,85</t>
+          <t>-34,37; 191,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-19,29; 163,93</t>
+          <t>-21,88; 167,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>56,4; 287,52</t>
+          <t>55,7; 294,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-72,98; 56,9</t>
+          <t>-72,95; 57,75</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,97; 40,47</t>
+          <t>-9,99; 41,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 36,03</t>
+          <t>-5,47; 36,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 34,78</t>
+          <t>-6,65; 34,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 14,91</t>
+          <t>-2,23; 14,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-29,48; 267,33</t>
+          <t>-28,83; 315,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-45,8; 644,56</t>
+          <t>-54,34; 654,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-14,54; 139,97</t>
+          <t>-16,25; 131,0</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,83; 13,43</t>
+          <t>2,47; 13,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,2; 17,12</t>
+          <t>5,75; 16,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,53; 19,23</t>
+          <t>10,05; 19,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 17,44</t>
+          <t>-8,14; 17,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,68; 57,16</t>
+          <t>8,53; 58,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,39; 74,69</t>
+          <t>18,9; 71,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,41; 105,39</t>
+          <t>43,24; 105,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-27,39; 71,55</t>
+          <t>-30,78; 69,73</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/LAWTONB_2R2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/LAWTONB_2R2-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14,96</t>
+          <t>15,41</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>40,89%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 12,2</t>
+          <t>0,1; 12,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,45; 16,38</t>
+          <t>3,35; 16,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,58; 18,01</t>
+          <t>5,13; 17,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,54; 20,17</t>
+          <t>9,94; 21,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,37; 46,7</t>
+          <t>-0,08; 50,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,82; 60,26</t>
+          <t>9,72; 60,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,95; 75,53</t>
+          <t>16,92; 74,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,83; 58,14</t>
+          <t>23,08; 61,88</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-3,43</t>
+          <t>8,16</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-20,79%</t>
+          <t>49,99%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 20,55</t>
+          <t>-8,12; 18,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 20,92</t>
+          <t>-3,0; 21,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,79; 26,14</t>
+          <t>8,32; 26,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,63; 9,02</t>
+          <t>2,92; 13,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-34,37; 191,09</t>
+          <t>-43,54; 155,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-21,88; 167,65</t>
+          <t>-17,94; 169,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,7; 294,92</t>
+          <t>52,89; 292,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-72,95; 57,75</t>
+          <t>13,12; 92,97</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,23</t>
+          <t>6,11</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>43,18%</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,99; 41,11</t>
+          <t>-8,59; 39,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 36,36</t>
+          <t>-7,59; 35,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 34,59</t>
+          <t>-6,7; 35,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 14,78</t>
+          <t>-1,99; 14,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-28,83; 315,15</t>
+          <t>-29,27; 258,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-54,34; 654,55</t>
+          <t>-51,72; 678,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-16,25; 131,0</t>
+          <t>-12,39; 136,35</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,92</t>
+          <t>16,61</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>67,47%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,47; 13,45</t>
+          <t>2,38; 13,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,75; 16,99</t>
+          <t>5,55; 16,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,05; 19,62</t>
+          <t>9,93; 19,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 17,1</t>
+          <t>13,14; 20,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,53; 58,15</t>
+          <t>5,96; 54,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,9; 71,74</t>
+          <t>17,9; 72,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,24; 105,09</t>
+          <t>42,16; 105,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-30,78; 69,73</t>
+          <t>49,14; 89,17</t>
         </is>
       </c>
     </row>
